--- a/psychologist_forms/003_student_mental_health_check_form--psychologist_forms.xlsx
+++ b/psychologist_forms/003_student_mental_health_check_form--psychologist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'normal',_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'normal', 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'anxious',_'label':_'anxious'}</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'anxious', 'label': 'Anxious'}</t>
+          <t>Anxious</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'depressed',_'label':_'depressed'}</t>
+          <t>depressed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'depressed', 'label': 'Depressed'}</t>
+          <t>Depressed</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'parent',_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'parent', 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'teacher',_'label':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'teacher', 'label': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'sleep',_'label':_'sleep_disturbances'}</t>
+          <t>sleep_disturbances</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'sleep', 'label': 'Sleep Disturbances'}</t>
+          <t>Sleep Disturbances</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'appetite',_'label':_'appetite_disturbances'}</t>
+          <t>appetite_disturbances</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'appetite', 'label': 'Appetite Disturbances'}</t>
+          <t>Appetite Disturbances</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'concentration',_'label':_'concentration_issues'}</t>
+          <t>concentration_issues</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'concentration', 'label': 'Concentration Issues'}</t>
+          <t>Concentration Issues</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'social',_'label':_'social_withdrawal'}</t>
+          <t>social_withdrawal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'social', 'label': 'Social Withdrawal'}</t>
+          <t>Social Withdrawal</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'follow-up',_'label':_'follow-up'}</t>
+          <t>follow-up</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'follow-up', 'label': 'Follow-up'}</t>
+          <t>Follow-up</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'counseling',_'label':_'counseling'}</t>
+          <t>counseling</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'counseling', 'label': 'Counseling'}</t>
+          <t>Counseling</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'no-action',_'label':_'no_action'}</t>
+          <t>no_action</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'no-action', 'label': 'No Action'}</t>
+          <t>No Action</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
